--- a/data/trans_orig/IP24_R2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP24_R2_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25257</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20547</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>29963</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,34%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>62,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>25352</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>19464</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>30929</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>45,27%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>34,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>55,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30679</t>
+          <t>21400</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24784</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36710</t>
+          <t>26175</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>51,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56032</t>
+          <t>46657</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48429</t>
+          <t>40238</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>64580</t>
+          <t>54249</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>47,11%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>54,78%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>23000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>18294</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27710</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,66%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>37,91%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>57,42%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>30648</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>25071</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>36536</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>54,73%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>44,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>65,24%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27892</t>
+          <t>29379</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21861</t>
+          <t>24604</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33787</t>
+          <t>33935</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>48,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>58539</t>
+          <t>52379</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49991</t>
+          <t>44787</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66142</t>
+          <t>58798</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>48257</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>48257</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>48257</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58571</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58571</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58571</t>
+          <t>50779</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>23667</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>17407</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>31069</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>15,06%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>11,08%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>19,77%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>33644</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>25463</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>45020</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>21,12%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>28,26%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>28912</t>
+          <t>25977</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>21525</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38030</t>
+          <t>32964</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>62556</t>
+          <t>49644</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>50409</t>
+          <t>39650</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>75926</t>
+          <t>59552</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>19,67%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>133496</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>126094</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>139756</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>80,23%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>88,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>209</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>125655</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>114279</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>133836</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>78,88%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>71,74%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>84,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>228</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>153178</t>
+          <t>119541</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>144060</t>
+          <t>112554</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160565</t>
+          <t>126162</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,18%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>278833</t>
+          <t>253037</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>265463</t>
+          <t>243129</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>290980</t>
+          <t>263031</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>86,9%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>157163</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>157163</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>157163</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>182090</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>182090</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>182090</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341389</t>
+          <t>302681</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341389</t>
+          <t>302681</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341389</t>
+          <t>302681</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>24420</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16911</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33569</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>12,26%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,49%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,86%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20884</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>14360</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>29329</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>12,07%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,3%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>16,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>28449</t>
+          <t>21454</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>19460</t>
+          <t>14669</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39250</t>
+          <t>30962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>49333</t>
+          <t>45874</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38591</t>
+          <t>35153</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>63543</t>
+          <t>57936</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>174743</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>165594</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>182252</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>87,74%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,14%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>91,51%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>152188</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>143743</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>158712</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>87,93%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>83,05%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>91,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>183104</t>
+          <t>153218</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172303</t>
+          <t>143710</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>192093</t>
+          <t>160003</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,8%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>335292</t>
+          <t>327961</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>321082</t>
+          <t>315899</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>346034</t>
+          <t>338682</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199163</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199163</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199163</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211553</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211553</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211553</t>
+          <t>174672</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>384625</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>384625</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>384625</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>42000</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>29698</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>65907</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,35%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>22,52%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>75515</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>47751</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>135168</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>27,41%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,34%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>49,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>47461</t>
+          <t>43254</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>33820</t>
+          <t>33760</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>79700</t>
+          <t>56351</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>122976</t>
+          <t>85255</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90361</t>
+          <t>69574</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>200561</t>
+          <t>114060</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>250645</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>226738</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>262947</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>85,65%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>77,48%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>89,85%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>283</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>199943</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>140290</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>227707</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>72,59%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>82,66%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>298</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>258022</t>
+          <t>213299</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>225783</t>
+          <t>200202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>271663</t>
+          <t>222793</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>83,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,91%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>457964</t>
+          <t>463943</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380379</t>
+          <t>435138</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>490579</t>
+          <t>479624</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>79,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>115344</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>98906</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>144738</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>16,54%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>14,19%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>20,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>185</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>155395</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>124635</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>229313</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>23,41%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>18,78%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>34,54%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>135501</t>
+          <t>112087</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115769</t>
+          <t>97037</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>128550</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>290896</t>
+          <t>227431</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>251372</t>
+          <t>204352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>362673</t>
+          <t>256861</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>19,39%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>783</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>581884</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>552490</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>598322</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>83,46%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>79,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>85,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>754</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>508434</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>434516</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>539194</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>76,59%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>65,46%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>81,22%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>783</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>622196</t>
+          <t>515435</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>589268</t>
+          <t>498972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>641928</t>
+          <t>530485</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,77%</t>
+          <t>79,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1130630</t>
+          <t>1097319</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1058853</t>
+          <t>1067889</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1170154</t>
+          <t>1120398</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,49%</t>
+          <t>80,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>84,57%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>757697</t>
+          <t>627522</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
